--- a/artfynd/A 40493-2024 artfynd.xlsx
+++ b/artfynd/A 40493-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -880,6 +880,112 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122249634</v>
+      </c>
+      <c r="B4" t="n">
+        <v>88589</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4412</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Äggvaxskivling</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hygrophorus karstenii</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skyltaren, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>579684</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6653552</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>

--- a/artfynd/A 40493-2024 artfynd.xlsx
+++ b/artfynd/A 40493-2024 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>122249634</v>
       </c>
       <c r="B4" t="n">
-        <v>88589</v>
+        <v>88596</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 40493-2024 artfynd.xlsx
+++ b/artfynd/A 40493-2024 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>122249634</v>
       </c>
       <c r="B4" t="n">
-        <v>88596</v>
+        <v>88598</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 40493-2024 artfynd.xlsx
+++ b/artfynd/A 40493-2024 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>122249634</v>
       </c>
       <c r="B4" t="n">
-        <v>88598</v>
+        <v>88614</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 40493-2024 artfynd.xlsx
+++ b/artfynd/A 40493-2024 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>122249634</v>
       </c>
       <c r="B4" t="n">
-        <v>88614</v>
+        <v>88624</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 40493-2024 artfynd.xlsx
+++ b/artfynd/A 40493-2024 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>122249634</v>
       </c>
       <c r="B4" t="n">
-        <v>88624</v>
+        <v>88636</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 40493-2024 artfynd.xlsx
+++ b/artfynd/A 40493-2024 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>122249634</v>
       </c>
       <c r="B4" t="n">
-        <v>88636</v>
+        <v>88640</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 40493-2024 artfynd.xlsx
+++ b/artfynd/A 40493-2024 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>122249634</v>
       </c>
       <c r="B4" t="n">
-        <v>88640</v>
+        <v>88645</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,11 +904,6 @@
       </c>
       <c r="E4" t="n">
         <v>4412</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Äggvaxskivling</t>
-        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>

--- a/artfynd/A 40493-2024 artfynd.xlsx
+++ b/artfynd/A 40493-2024 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>122249634</v>
       </c>
       <c r="B4" t="n">
-        <v>88645</v>
+        <v>88658</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,6 +904,11 @@
       </c>
       <c r="E4" t="n">
         <v>4412</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Äggvaxskivling</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>

--- a/artfynd/A 40493-2024 artfynd.xlsx
+++ b/artfynd/A 40493-2024 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>122249634</v>
       </c>
       <c r="B4" t="n">
-        <v>88658</v>
+        <v>88040</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 40493-2024 artfynd.xlsx
+++ b/artfynd/A 40493-2024 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>122249634</v>
       </c>
       <c r="B4" t="n">
-        <v>88040</v>
+        <v>88041</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 40493-2024 artfynd.xlsx
+++ b/artfynd/A 40493-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113270991</v>
+        <v>113271004</v>
       </c>
       <c r="B2" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579593</v>
+        <v>579635</v>
       </c>
       <c r="R2" t="n">
-        <v>6653501</v>
+        <v>6653589</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,53 +776,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113271115</v>
+        <v>122249634</v>
       </c>
       <c r="B3" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>4412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergsjön, Vstm</t>
+          <t>Skyltaren, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579960</v>
+        <v>579684</v>
       </c>
       <c r="R3" t="n">
-        <v>6653628</v>
+        <v>6653552</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-07-11</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-07-12</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122249634</v>
+        <v>113270991</v>
       </c>
       <c r="B4" t="n">
-        <v>88041</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,37 +888,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4412</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skyltaren, Vstm</t>
+          <t>Bergsjön, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579684</v>
+        <v>579593</v>
       </c>
       <c r="R4" t="n">
-        <v>6653552</v>
+        <v>6653501</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,12 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2023-07-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2023-07-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,6 +971,653 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122249635</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skyltaren, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>579703</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6653500</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122273458</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skyltaren, ca 130 m O om sjöns norra spets (knärot), Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>579704</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6653500</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>U-Sal-1137</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>proj. Värdefulla skogsmiljöer i  Västmanlands län</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Bo Eriksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>113271082</v>
+      </c>
+      <c r="B7" t="n">
+        <v>85534</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>241</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gransotdyna</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Camarops tubulina</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Shear</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bergsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>579997</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6653588</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-07-11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-07-12</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>113271005</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bergsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>579984</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6653580</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-07-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-07-12</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>113271115</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bergsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>579960</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6653628</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-07-11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-07-12</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>113271033</v>
+      </c>
+      <c r="B10" t="n">
+        <v>75300</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bergsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>579940</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6653685</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-07-11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-07-12</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>al</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
         <is>
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>

--- a/artfynd/A 40493-2024 artfynd.xlsx
+++ b/artfynd/A 40493-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113270991</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,6 +897,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122249635</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122273458</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113271082</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1213,6 +1238,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113271004</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113271005</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1415,6 +1450,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113271115</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1516,6 +1556,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122249634</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1622,8 +1667,24 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113271033</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>